--- a/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>EC</t>
   </si>
@@ -656,540 +656,553 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11693300</v>
+      </c>
+      <c r="E8" s="3">
         <v>7819800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7642900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7594400</v>
       </c>
-      <c r="G8" s="3">
-        <v>7265800</v>
-      </c>
       <c r="H8" s="3">
+        <v>7265600</v>
+      </c>
+      <c r="I8" s="3">
         <v>7478500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7890100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8300800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7888400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8112400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8981500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8683800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8219600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8393000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9522700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10859600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11410100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8442900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7622700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5133200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4083300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3613300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2979900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2957500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2026000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3918700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4831100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4863900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4943300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4304500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4761700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4826500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9488900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4392800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>4916200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4263900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>4208300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4278900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4393300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4020500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6879300</v>
+      </c>
+      <c r="E9" s="3">
         <v>4683700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5273300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4964900</v>
       </c>
-      <c r="G9" s="3">
-        <v>5087200</v>
-      </c>
       <c r="H9" s="3">
+        <v>5087300</v>
+      </c>
+      <c r="I9" s="3">
         <v>4844500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5415500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5242600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5061700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4857400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5915000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5003200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5069300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4846100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5761800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6108800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>6000200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4663800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4591800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3191300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2400600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2207500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2164400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2002500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1827700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2934600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3190200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3034900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3027600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2763200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3105100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2868100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5581200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2654000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3118400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2808700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2952200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2926600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3202400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2883800</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4814000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3136100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2369600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2629500</v>
       </c>
-      <c r="G10" s="3">
-        <v>2178500</v>
-      </c>
       <c r="H10" s="3">
+        <v>2178300</v>
+      </c>
+      <c r="I10" s="3">
         <v>2634000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2474600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3058200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2826700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3255000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3066500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3680700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3150200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3546900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3760900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4750800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5409900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3779100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3030900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1941900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1682700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1405700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>815500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>955000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>198300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>984100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1641000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1829000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1915700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1541300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1656600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1958400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3907700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1738700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1797800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1455200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1256100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1352300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1190900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1136600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,8 +1245,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1276,86 +1290,89 @@
       <c r="P12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="R12" s="3">
         <v>209900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>24900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>115700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>101600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>66200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>14100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>35300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>86600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>23800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>33600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>103000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>15700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>66900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>16600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>50300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>271600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>56400</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>21200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>292200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>103900</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>24700</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>8600</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>96800</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,252 +1493,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-137100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>28000</v>
       </c>
-      <c r="G14" s="3">
-        <v>53300</v>
-      </c>
       <c r="H14" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I14" s="3">
         <v>3800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-295700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>35700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-68500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>81100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>24000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-116500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-328800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>314200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>187600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>10400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>149000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-26200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-14700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-34600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-556400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>7900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-12900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>800</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>244000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1075700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1006900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>71900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1047600</v>
       </c>
-      <c r="G15" s="3">
-        <v>1141900</v>
-      </c>
       <c r="H15" s="3">
+        <v>1162200</v>
+      </c>
+      <c r="I15" s="3">
         <v>931300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>75500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1042600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>979600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>995100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>555900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1050500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>833800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>715100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>79300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>31900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>34000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>33800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>89200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>12600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>14100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>13600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>40200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>12900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>20000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>46000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>10700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>11200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>4500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>6100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>8700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>15000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>10900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>13300</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>16400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1787,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7967200</v>
+      </c>
+      <c r="E17" s="3">
         <v>5479700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6367300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5699600</v>
       </c>
-      <c r="G17" s="3">
-        <v>5832100</v>
-      </c>
       <c r="H17" s="3">
+        <v>5878500</v>
+      </c>
+      <c r="I17" s="3">
         <v>5476600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5959500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6033000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5569000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5560400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7522300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5831500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5691800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5426800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6706600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6554200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6572100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5185200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5129400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3570700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2706400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2455500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2553800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2319800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1827300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3529200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3845900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3321700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3334800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2966200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3593200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3300300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6019600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2838800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3111000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3200600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3162600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>3223200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>3854400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>3182100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3726000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2340100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1275600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1894800</v>
       </c>
-      <c r="G18" s="3">
-        <v>1433700</v>
-      </c>
       <c r="H18" s="3">
+        <v>1387000</v>
+      </c>
+      <c r="I18" s="3">
         <v>2001900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1930600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2267900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2319400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2552000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1459200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2852300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2527800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2966100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2816100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4305400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4838000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3257700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2493200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1562500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1376900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1157800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>426100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>637700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>198700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>389600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>985200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1542100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1608600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1338300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1168600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1526200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3469300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1554000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1805100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1063300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1045700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1055600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>538900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>838400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,618 +2082,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E20" s="3">
         <v>262300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>79000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>46100</v>
       </c>
-      <c r="G20" s="3">
-        <v>78800</v>
-      </c>
       <c r="H20" s="3">
+        <v>78600</v>
+      </c>
+      <c r="I20" s="3">
         <v>157400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>107900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>128800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>126300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>121800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-206800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>157700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>65800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-44700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-109400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-58100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-21600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>25500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-34100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>70200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-70500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>31500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-47000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>80100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-31700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>43400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>61300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>83200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>19300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>45700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>26900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>18100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-58800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>117200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-111000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>291700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-29900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4762500</v>
+      </c>
+      <c r="E21" s="3">
         <v>3084700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1268500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2896400</v>
       </c>
-      <c r="G21" s="3">
-        <v>2496800</v>
-      </c>
       <c r="H21" s="3">
+        <v>2470700</v>
+      </c>
+      <c r="I21" s="3">
         <v>2775900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1898100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3181600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3172700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3425300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2009900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4109600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3203800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3685700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3693000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5056700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5471100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3904100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3137800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2179000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1845800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1632900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1019600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1118900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>779700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>922300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1657500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2106000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2217200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1937100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1748700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2104600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4627400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2118200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2411200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1718300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1846200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1604900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1464900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1499400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>505300</v>
+      </c>
+      <c r="E22" s="3">
         <v>484100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>492500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>501600</v>
       </c>
-      <c r="G22" s="3">
-        <v>470600</v>
-      </c>
       <c r="H22" s="3">
+        <v>470700</v>
+      </c>
+      <c r="I22" s="3">
         <v>442100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>464900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>438900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>430100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>445300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>457600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>425800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>404900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>375500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>391500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>363900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>346400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>285600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>294600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>154300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>127500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>117300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>125700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>155400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>156700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>126200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>127000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>128100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>129500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>122000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>183100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>144600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>347900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>171800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>206800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>198200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>153300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>205200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>226800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>252900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>3282100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1660400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>921000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1393700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>916100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1471400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1746900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1768000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1845700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2072600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1116600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2792100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2063300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2712500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2490400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3896800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4382200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2914000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2177000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1433600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1215200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1032100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>370700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>411700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>73500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>216300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>938200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1382300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1522500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1277600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1068600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1401000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3167100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1409100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1616500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>806300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1009600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>739400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>603800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>555500</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1219700</v>
+      </c>
+      <c r="E24" s="3">
         <v>616300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>263600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>435200</v>
       </c>
-      <c r="G24" s="3">
-        <v>314300</v>
-      </c>
       <c r="H24" s="3">
+        <v>314700</v>
+      </c>
+      <c r="I24" s="3">
         <v>462300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>606200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>543000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>781700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>757000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-194300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1311900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>799400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1208200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>643600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1278900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1380500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1009800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>495300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>482700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>371200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>322700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>178300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>137100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>91500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-186900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>477900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>505400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>451800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>303400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>589000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1192000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>564000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>457200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>414600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>535100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>396300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>485600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>408300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2830,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2062400</v>
+      </c>
+      <c r="E26" s="3">
         <v>1044100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>657400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>958500</v>
       </c>
-      <c r="G26" s="3">
-        <v>601700</v>
-      </c>
       <c r="H26" s="3">
+        <v>601400</v>
+      </c>
+      <c r="I26" s="3">
         <v>1009100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1140700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1225000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1063900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1315600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1311000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1480200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1263900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1504300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1846800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2617900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3001700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1904200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1681700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>951000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>844000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>709400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>192400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>274600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>72400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>124800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1125100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>904500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1017100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>825800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>765200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>811900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1975100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>845100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1159300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>391700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>474500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>343200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>118200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>147200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1764000</v>
+      </c>
+      <c r="E27" s="3">
         <v>788700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>405000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>652300</v>
       </c>
-      <c r="G27" s="3">
-        <v>443800</v>
-      </c>
       <c r="H27" s="3">
+        <v>443500</v>
+      </c>
+      <c r="I27" s="3">
         <v>745600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>884000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>875200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>816300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1039700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1091500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1257200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>979500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1222700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1644200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2378200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2722200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1708900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1458500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>837600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>782100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>648000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>141800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>205200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>34600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1042300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>813000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>941500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>741000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>688300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>749200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1840300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>784400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1096500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>321100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>417500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>283500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>61400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3205,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3269,8 +3330,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3391,8 +3455,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3513,252 +3580,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-262300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-79000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-46100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-78800</v>
-      </c>
       <c r="H32" s="3">
+        <v>-78600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-157400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-107900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-128800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-126300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-121800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>206800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-157700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-65800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>44700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>109400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>58100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>21600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-25500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>34100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>8400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-70200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>70500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-31500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>47000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-80100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>31700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-43400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-61300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-83200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-19300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-45700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-26900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-18100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>58800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-117200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>111000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-291700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1764000</v>
+      </c>
+      <c r="E33" s="3">
         <v>788700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>405000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>652300</v>
       </c>
-      <c r="G33" s="3">
-        <v>443800</v>
-      </c>
       <c r="H33" s="3">
+        <v>443500</v>
+      </c>
+      <c r="I33" s="3">
         <v>745600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>884000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>875200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>816300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1039700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1091500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1257200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>979500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1222700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1644200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2378200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2722200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1708900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1458500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>837600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>782100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>648000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>141800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>205200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>34600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1042300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>813000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>941500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>741000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>688300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>749200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1840300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>784400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1096500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>321100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>417500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>283500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>61400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3879,257 +3955,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1764000</v>
+      </c>
+      <c r="E35" s="3">
         <v>788700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>405000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>652300</v>
       </c>
-      <c r="G35" s="3">
-        <v>443800</v>
-      </c>
       <c r="H35" s="3">
+        <v>443500</v>
+      </c>
+      <c r="I35" s="3">
         <v>745600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>884000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>875200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>816300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1039700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1091500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1257200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>979500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1222700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1644200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2378200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2722200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1708900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1458500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>837600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>782100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>648000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>141800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>205200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>34600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1042300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>813000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>941500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>741000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>688300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>749200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1840300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>784400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1096500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>321100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>417500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>283500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>61400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4172,8 +4257,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4216,1106 +4302,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>2543900</v>
+      </c>
+      <c r="E41" s="3">
         <v>3518500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2836100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2637700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2477800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3362500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3187100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3381700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3200300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3930800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3184300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2983700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2713800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3347700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3696300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3229400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2626900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3639800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3492000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2219100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1054500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1404400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1067300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1878900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2219500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2287300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1839700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2446500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1491500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2413200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1641100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1922600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1901200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2359900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1755700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1832500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1501600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1561700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1095700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1691700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>711800</v>
+      </c>
+      <c r="E42" s="3">
         <v>249100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>487400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>857700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1034000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>602700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>193000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>537100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>510800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>441500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>480400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>433100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>218400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>363800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>400600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>672700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>431200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>560000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>517100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>467300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>102400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>156800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>506700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>839200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>999800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>247600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>459900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>662000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>906600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1349100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1383500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>2042100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1878800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1325000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1736700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1560200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1118400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>3310400</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>3450900</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>2458300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>10132100</v>
+      </c>
+      <c r="E43" s="3">
         <v>8065600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7795400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8009500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7523900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7771100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7226100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7387300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7745000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11217900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10692300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11260800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12220100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>11822500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11251700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9999900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9332300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7984900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6087200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5301400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3306500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2555100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1960700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2097900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2059500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1806900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2131500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2049800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2634900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2725700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2538700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2350500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2628100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2269200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2341000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1905300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1705700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2007700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>2235000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>3076500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2838300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2283100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2682200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2546300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2630500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2274100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2616200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2748600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2802500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2633600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2807200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2467200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2402800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2851200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2695900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3165900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2852700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2015600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1997200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1507200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1345600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1061300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1322500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1208400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1511100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1471100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1594800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1580600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1479100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1326100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1461500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1641500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1478800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1472400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1512100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1366100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1385800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1267800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1075500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>546600</v>
+      </c>
+      <c r="E45" s="3">
         <v>485700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>485600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>584900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>588100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>546500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>510300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>574100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>638200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>632900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>517500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>556300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>598700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>556400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>346700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>405200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>306400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>341400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>295100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>358600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>175900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>224100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>199200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>282900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>216900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>304500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>172500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>196300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>144400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>146700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>138600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>131000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>125000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>131300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>125800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>180600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>191400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>169900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>140500</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>313400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>17334800</v>
+      </c>
+      <c r="E46" s="3">
         <v>15534100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14173800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15211700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14490000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15258700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13752300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14835800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15013700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19207200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17711700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18275700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18365100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18650500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18546400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17003100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15862700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15378800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12407000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>10343600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6146600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5686000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4795200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6421200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6704100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6157500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6074800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6949500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6758000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8113900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>7028000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>7907800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8174700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7564200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7431700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>7064000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6082800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>8133400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>7962600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>7773800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2722800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2635400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2521000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2990700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3088700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2927800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2957400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3061800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2228400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2335200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2269100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2243600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2379700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2169700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10371700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9597600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9415100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9386800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8117900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7244100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1100900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1015100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>992900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1208900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1451100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1642600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1920700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1956400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1743300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1335500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1410900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1531900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1627300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1929500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1815500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1384000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1419900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1466400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1205600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1328900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>44490200</v>
+      </c>
+      <c r="E48" s="3">
         <v>42395200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41240400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38724200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>37415500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36640300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35400300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35360500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35454400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36778400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36455600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34609400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33539900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>31065700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34547700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34531700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>33960900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>32323000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30365200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>25704900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21623400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21324800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20752300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>24092400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>23977800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>26598600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>24369500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>24227100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>23212000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>23085100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>22319900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>22118800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>24635700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>24041100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>26453800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>25781800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>26507600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>26236200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>27921300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>27732000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>5075500</v>
+      </c>
+      <c r="E49" s="3">
         <v>4977900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4941300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4874300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4868400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4853100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4834500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4918100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4937100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5013600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4987400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5014100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5012800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4875200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5581500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5565400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5331700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4982500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4626800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6636400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>407900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>402700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>400900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>460900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>357200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>397400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>364700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>355300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>354900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>361500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>345800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>354300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>383600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>384100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>415900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>404900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>375200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>380300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>393200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5436,8 +5550,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5558,130 +5675,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1661000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1587200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1522300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1483300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1437700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4884000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1308300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5152300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5187700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4681600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1390700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3707800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4043600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4335700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4481300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4085100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3777700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3144900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3103100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3142400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2484600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2427200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2336300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2923900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2825800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3302800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2486900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1880600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1713700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1711100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1717900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1535300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1653700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1652100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2499000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2571300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2636600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2342900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2548600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>2709300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5802,130 +5925,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>82642200</v>
+      </c>
+      <c r="E54" s="3">
         <v>78567400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75353900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>74282800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72146400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71607200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>68338200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70209700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69221700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74817800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>72865400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70505000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>70224100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>67474900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>73528700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>70783000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>68348000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>65215900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58620000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>53071400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31763400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>30855800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>29277600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>35107300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>35316000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>38098900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>35216500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>35368900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33781800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>34607100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>32822600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>33448100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>36475000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>35571100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>38615900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>37205900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>37022200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>38559200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>40031400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>39970100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5968,8 +6097,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6012,740 +6142,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>3746400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3284200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3085900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2939500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2794000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2866300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3432700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2979200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2852300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3047300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3554400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2988400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2769200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2806000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3608300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2945100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3181400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2864600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2512900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1848600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1513700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1410300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1363300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1292100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1131100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1753800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2109900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1923100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1823000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1658600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1788400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1669000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1569200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1386700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1628500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1347100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1319700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1235200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1540900</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1802300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>3218100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3334700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2673200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3169900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3830000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3109400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2559900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2837800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3877900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3979100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4013900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4354600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4098000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3511800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5327700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5653600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2538400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2272100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2209500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1903900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1117900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1093400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1033900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1497800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2281900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1593000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1303200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1221700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1103800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1091500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1045200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2169300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1703100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1479900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1646200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1636800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1254200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1310400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1361600</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1668900</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>3558500</v>
+      </c>
+      <c r="E59" s="3">
         <v>4776300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2363500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2916100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2580100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4732500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2168000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2172900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2643500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6397400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2816200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4629600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7606000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9319000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4691800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4248500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5135800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5984500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2537300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2381300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1427600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1688500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1442100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2328000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2975500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4170100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2239900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1948300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2444200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4481500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1800800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2086300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2384800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3290800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2116200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2184600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2070100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2920300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2505200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1795500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>11469900</v>
+      </c>
+      <c r="E60" s="3">
         <v>12342000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9153200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9953700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9964300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11477700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8988100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8855900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10120600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14671900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11245100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12785000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>15137600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16312800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13627800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12847200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10855500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11121200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7259700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>6133800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4059200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4192300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3839300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5117900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6388500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>7517000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5653000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5093100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5371000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>7231700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4634400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5924600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5657100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6157300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5390900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5168500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4644100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>5465900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>5407800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>5266700</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>27301700</v>
+      </c>
+      <c r="E61" s="3">
         <v>26202500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26286900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25912400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25620000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25183600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24645500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25079000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23930800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24196400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23300300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22769000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21797100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21624200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22304700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21281400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23135700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21548700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20605100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18309500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>9394800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>9384300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>8779800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>11336200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>10598900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>10485200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8639000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>9688200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9012400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9095000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8851100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8601200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>10695600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>10807900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>12289100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>12638500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>13502000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>14821200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>15871600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>15481100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>5565600</v>
+      </c>
+      <c r="E62" s="3">
         <v>5180600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5005700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4501200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4244400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6979900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3867200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7550400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7462400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7807500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4909800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6892800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6780000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5967400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>9015300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9694700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>9740800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>9368600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>8254700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7994800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5164400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5067400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4936500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4931700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4975800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>5437900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>5235000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4019500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4026100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4060300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3917900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4026500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4451000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4256600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5005900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>4070100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3843000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3738900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3796500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>3809200</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6866,8 +7015,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7140,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7110,130 +7265,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>50760400</v>
+      </c>
+      <c r="E66" s="3">
         <v>49938500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>46381600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47048300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46291000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46977300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>43398000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>45043200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>45310200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>50670800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>46252400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>44794700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>45902800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>45943300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51680400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>50316600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>49990000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>47937600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>41404100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>39212600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>19406800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>19405700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>18337600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22287100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22919800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>24429400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>20549300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19382000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19002400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>20923200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>17947000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19039000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21376300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>21713500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>23288300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>22436200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>22579500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>24545600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>25619100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>25118300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7276,8 +7437,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7398,8 +7560,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7520,8 +7685,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7642,8 +7810,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7764,130 +7935,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>13011600</v>
+      </c>
+      <c r="E72" s="3">
         <v>10563000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10808300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9983700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8978700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8310200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9190200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8785000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7997600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7698100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9943200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8476400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6998700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5425900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10521600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>9247300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7143800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6217600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6914900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4951900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3927300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3144800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2643400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2859000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2653800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2868400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4758100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4799200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3986200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3044700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4623800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4086800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3708300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2652600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3163800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2067600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1746600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1329000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1390300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1327600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -8008,8 +8185,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8130,8 +8310,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8252,130 +8435,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>24707800</v>
+      </c>
+      <c r="E76" s="3">
         <v>21785000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22213400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20542100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19401200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18475300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18980600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18774900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17827600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17944600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20235400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19310300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17932400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15684500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21848300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20466300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18358000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17278400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17215900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13858900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12356600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11450100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10940000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12820300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12396200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13669400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14667200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15986900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14779400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13683900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14875500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14409100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>15098700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13857600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15327600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14769700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>14442700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14013600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>14412400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>14851800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8496,257 +8685,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1764000</v>
+      </c>
+      <c r="E81" s="3">
         <v>788700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>405000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>652300</v>
       </c>
-      <c r="G81" s="3">
-        <v>443800</v>
-      </c>
       <c r="H81" s="3">
+        <v>443500</v>
+      </c>
+      <c r="I81" s="3">
         <v>745600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>884000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>875200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>816300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1039700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1091500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1257200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>979500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1222700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1644200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2378200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2722200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1708900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1458500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>837600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>782100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>648000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>141800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>205200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>34600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1042300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>813000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>941500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>741000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>688300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>749200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1840300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>784400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1096500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>321100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>417500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>283500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>61400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8789,130 +8987,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>1100500</v>
+      </c>
+      <c r="E83" s="3">
         <v>927500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>692400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>960500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>897900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>926000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>737500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>874800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>805500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>683200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>525300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>691800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>684600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>722000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>811100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>796000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>742600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>704500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>666200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>591000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>503100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>483400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>523300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>551700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>549500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>579700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>592200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>595600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>565200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>537500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>497000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>559000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1112400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>537300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>588000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>713800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>683300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>660300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>634300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>690900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9033,8 +9235,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9155,8 +9360,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9277,8 +9485,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9399,8 +9610,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9521,130 +9735,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>2024900</v>
+      </c>
+      <c r="E89" s="3">
         <v>1960900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2199900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2259700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2460100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1459700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2172100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2989900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4126900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1558800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2685000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1035700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>752000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>447400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2726200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3733800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1600000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>984400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2642300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1161500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>695900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>616000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1120400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>846400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-539500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>668800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1966900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2513500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1620900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1305300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1176500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2309500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2794100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1401900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2033100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1494000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>478900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1425500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1328000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1926000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9687,130 +9907,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1137700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1124100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1748000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1260700</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1195200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-1467400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-927000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1698300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1182300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1076300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1052300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1783400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1508300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1279700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1068800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8443313000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5493938000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4586132000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3354387000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4542147000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3564839000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-295700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-178500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-359700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-320800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-278300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-214000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-385700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-324300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-196700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-161900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-220300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-333000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-133100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-305300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-160000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-200100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-90800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-743300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-691400</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9931,8 +10155,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10053,130 +10280,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1484100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-819500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-857400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-795800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-1490000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1489900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1303800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1412100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1744400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1039100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1693900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1289200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1079500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-807400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1689300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1203900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-900300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-722400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-916800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2943100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-552000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-145300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-462600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-40800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1270000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-224600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1183000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-712600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-475200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-293400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>130100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-973300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1661300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1079400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1135300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-623200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1472300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1116600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-834500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1463100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10219,130 +10452,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="3">
+        <v>1410000</v>
+      </c>
+      <c r="E96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>100</v>
       </c>
-      <c r="G96" s="3">
-        <v>2151000</v>
-      </c>
       <c r="H96" s="3">
+        <v>1980400</v>
+      </c>
+      <c r="I96" s="3">
         <v>166200</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>535900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2555500</v>
       </c>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>236800</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>559200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>49000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-520800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1305400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1479900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-71100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-323200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-60300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-206300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-35300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-732400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-698500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-458600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-110700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-990600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-832000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1793500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-36500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-494600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-736600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-63900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-53900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-327100</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-36600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-105500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-95000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10463,8 +10700,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10585,8 +10825,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10707,370 +10950,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1604300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-532400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1038000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1320100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-1883600</v>
-      </c>
       <c r="H100" s="3">
+        <v>-1883700</v>
+      </c>
+      <c r="I100" s="3">
         <v>-136400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-831800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1174600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3560500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>156700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-523500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-536400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>407500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-627800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1842900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1924100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-402100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-734000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2906600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-507400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-163600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1135500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1148900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2061800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-266700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1261300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-954100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2097800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-274300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1624700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1176600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1555200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-273900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-877700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-278100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2634600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-294000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-619400</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-62200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-8100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>61700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>136000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>61000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>57300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-399200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-62700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-136000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-26700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>160600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>14300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>195100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>186800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>16500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>211600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>79700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-10700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>13700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>30000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-99000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-144100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>270100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-38800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>108200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>30500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-28500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>107900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>51800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-60100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-72400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>9800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-78800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>69600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-93500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>51000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-1202800</v>
+      </c>
+      <c r="E102" s="3">
         <v>597200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>87500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>62700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-975600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>206800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-466600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>733700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>68500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>184400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-999900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>20800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>596000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>703500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1012800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-143200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1071100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1114400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-349900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>337100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-576700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-340600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>108200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>447600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-516200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>955000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-921700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>709100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-210300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>211400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-482500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-23800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>30000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>513900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-613900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>230300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-67900</v>
       </c>
     </row>
